--- a/output/graficos_nacionales/plot_nacional_d_residentes_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_residentes_a_2022.xlsx
@@ -2149,7 +2149,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:48</t>
+    <t xml:space="preserve">2026-09-15 11:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_d_residentes_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_residentes_a_2022.xlsx
@@ -2149,7 +2149,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-15 11:08</t>
+    <t xml:space="preserve">2026-09-24 00:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
